--- a/data/raw/RPi_Pico_W_Official.xlsx
+++ b/data/raw/RPi_Pico_W_Official.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\szb75\Documents\Other_Proj\ArchitecturalCarbonModelingTool\ACT\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F31162F-D9A2-4DB9-8C92-A6A2116C1894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C1AC13C-FC71-4ABD-9C83-1E459AAD0A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-18120" windowWidth="29040" windowHeight="17520" xr2:uid="{EFECAB25-8862-4039-872A-9D66B4D0B167}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{EFECAB25-8862-4039-872A-9D66B4D0B167}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -797,7 +794,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
   </numFmts>
   <fonts count="17" x14ac:knownFonts="1">
     <font>
@@ -1000,7 +997,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1028,113 +1025,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Results"/>
-      <sheetName val="HotCarbon_Results"/>
-      <sheetName val="DecemberResults"/>
-      <sheetName val="Rasberry Pi Results"/>
-      <sheetName val="ICs"/>
-      <sheetName val="RPi ICs"/>
-      <sheetName val="reference"/>
-      <sheetName val="Methodology"/>
-      <sheetName val="Max Power Draw"/>
-      <sheetName val="Arduino Nano 33 BLE Sense With "/>
-      <sheetName val="Arduino Nano 33 BLE Sense NINA-"/>
-      <sheetName val="Arduino Uno R3"/>
-      <sheetName val="Analog Devices Max78000FTHR"/>
-      <sheetName val="Coral Dev Micro"/>
-      <sheetName val="nRF52840 Minimal"/>
-      <sheetName val="Adafruit HUZZAH32 – ESP32"/>
-      <sheetName val="STM32F411E"/>
-      <sheetName val="Copy of STM32F411E"/>
-      <sheetName val="RPi 4 BoM Official"/>
-      <sheetName val="RPi 4 LCA Calculations"/>
-      <sheetName val="RPi 4 Comparison"/>
-      <sheetName val="RPi Official 3A+"/>
-      <sheetName val="Raspberry Pi 3 A+"/>
-      <sheetName val="Raspberry Pi Pico"/>
-      <sheetName val="Raspberry Pi Pico W"/>
-      <sheetName val="RPi Pico W Official"/>
-      <sheetName val="RPi Pico W Comparison"/>
-      <sheetName val="Raspberry Pi Pico 2"/>
-      <sheetName val="Pico Minimal"/>
-      <sheetName val="Minimal v Board"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25">
-        <row r="3">
-          <cell r="F3" t="str">
-            <v>RP2040 - RP2B1MicroController</v>
-          </cell>
-          <cell r="N3">
-            <v>2.7223428430714701E-2</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="F4" t="str">
-            <v>Buck bosst switchmode PSU</v>
-          </cell>
-          <cell r="N4">
-            <v>2.5415230232364645E-2</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="F5" t="str">
-            <v>Serial NOR Flash, QSPI, 16MBit, 8-pin USON 2x3mm 133MHz</v>
-          </cell>
-          <cell r="N5">
-            <v>3.0000000000000001E-5</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="F6" t="str">
-            <v>BT WIFI FM Combo</v>
-          </cell>
-          <cell r="N6">
-            <v>6.4557524875935024E-2</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1458,7 +1348,7 @@
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.6328125" customWidth="1"/>
-    <col min="3" max="3" width="17.08984375" customWidth="1"/>
+    <col min="3" max="3" width="20.90625" customWidth="1"/>
     <col min="4" max="4" width="23.453125" customWidth="1"/>
     <col min="5" max="5" width="18.36328125" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
